--- a/resources/templates/heyman/roro_contract.xlsx
+++ b/resources/templates/heyman/roro_contract.xlsx
@@ -25,7 +25,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Ssancar LTD. Cho Tae Shin. 499, Aam-dero, Yeonsu-gu, Incheon, Korea  Phone: +82-505-366-9977 Email: ssancar9977@gmail.com</t>
+      <t xml:space="preserve">HEYMAN LTD., 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Republic of Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : man99777@naver.com</t>
     </r>
   </si>
   <si>
@@ -1580,7 +1580,7 @@
       <c r="A2" s="37" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Ssancar LTD. Cho Tae Shin. 499, Aam-dero, Yeonsu-gu, Incheon, Korea  Phone: +82-505-366-9977 Email: ssancar9977@gmail.com</t>
+            <t xml:space="preserve">HEYMAN LTD., 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Republic of Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : man99777@naver.com</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/roro_contract.xlsx
+++ b/resources/templates/heyman/roro_contract.xlsx
@@ -25,7 +25,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">HEYMAN LTD., 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Republic of Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : man99777@naver.com</t>
+      <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
     </r>
   </si>
   <si>
@@ -1580,7 +1580,7 @@
       <c r="A2" s="37" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">HEYMAN LTD., 163 Sangidaehak-ro, Siheung-si, Gyeonggi-do, Republic of Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : man99777@naver.com</t>
+            <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
           </r>
         </is>
       </c>

--- a/resources/templates/heyman/roro_contract.xlsx
+++ b/resources/templates/heyman/roro_contract.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
   <si>
     <r>
       <t xml:space="preserve">PROFORM CONTRACT</t>
@@ -130,6 +130,9 @@
     <r>
       <t xml:space="preserve">Beneficiary Adress</t>
     </r>
+  </si>
+  <si>
+    <t>#513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea</t>
   </si>
   <si>
     <r>
@@ -447,7 +450,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -851,17 +854,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFAEAAAA"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -878,7 +870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="77">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -1074,12 +1066,6 @@
     <xf xfId="0" fontId="14" numFmtId="0" fillId="0" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="1" numFmtId="166" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -1104,7 +1090,7 @@
     <xf xfId="0" fontId="2" numFmtId="165" fillId="6" borderId="22" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="33" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="32" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="165" fillId="6" borderId="5" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1801,14 +1787,16 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="66"/>
+      <c r="F13" s="61" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="61"/>
       <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="13.5" s="52" customFormat="1">
       <c r="A14" s="8"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="67"/>
+      <c r="E14" s="65"/>
       <c r="G14" s="21"/>
       <c r="J14" s="52"/>
     </row>
@@ -1893,10 +1881,10 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="68">
+      <c r="F16" s="66">
         <v>2300</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="67">
         <v>1075</v>
       </c>
       <c r="I16" s="28" t="str">
@@ -1934,10 +1922,10 @@
           </r>
         </is>
       </c>
-      <c r="F17" s="68">
+      <c r="F17" s="66">
         <v>6400</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="67">
         <v>1075</v>
       </c>
       <c r="I17" s="28" t="str">
@@ -1975,10 +1963,10 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="68">
+      <c r="F18" s="66">
         <v>5100</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="67">
         <v>1075</v>
       </c>
       <c r="I18" s="28" t="str">
@@ -2016,10 +2004,10 @@
           </r>
         </is>
       </c>
-      <c r="F19" s="68">
+      <c r="F19" s="66">
         <v>1600</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="67">
         <v>1075</v>
       </c>
       <c r="I19" s="28" t="str">
@@ -2037,8 +2025,8 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
-      <c r="F20" s="70"/>
-      <c r="G20" s="71"/>
+      <c r="F20" s="68"/>
+      <c r="G20" s="69"/>
       <c r="I20" s="28" t="str">
         <f>F20+G20</f>
         <v>0</v>
@@ -2054,8 +2042,8 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
-      <c r="F21" s="70"/>
-      <c r="G21" s="71"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="69"/>
       <c r="I21" s="28" t="str">
         <f>F21+G21</f>
         <v>0</v>
@@ -2071,8 +2059,8 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="71"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="69"/>
       <c r="I22" s="28" t="str">
         <f>F22+G22</f>
         <v>0</v>
@@ -2088,8 +2076,8 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="71"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="69"/>
       <c r="I23" s="28" t="str">
         <f>F23+G23</f>
         <v>0</v>
@@ -2111,8 +2099,8 @@
           </r>
         </is>
       </c>
-      <c r="F24" s="70"/>
-      <c r="G24" s="71"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="69"/>
       <c r="I24" s="28" t="str">
         <f>F24+G24</f>
         <v>0</v>
@@ -2128,8 +2116,8 @@
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="71"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="69"/>
       <c r="I25" s="28" t="str">
         <f>F25+G25</f>
         <v>0</v>
@@ -2145,8 +2133,8 @@
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="73"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="71"/>
       <c r="H26" s="52"/>
       <c r="I26" s="28" t="str">
         <f>F26+G26</f>
@@ -2163,8 +2151,8 @@
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="73"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="71"/>
       <c r="H27" s="52"/>
       <c r="I27" s="28" t="str">
         <f>F27+G27</f>
@@ -2181,8 +2169,8 @@
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="73"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="71"/>
       <c r="H28" s="52"/>
       <c r="I28" s="28" t="str">
         <f>F28+G28</f>
@@ -2199,8 +2187,8 @@
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="17"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="73"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="71"/>
       <c r="H29" s="52"/>
       <c r="I29" s="28" t="str">
         <f>F29+G29</f>
@@ -2217,8 +2205,8 @@
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="17"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="73"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="71"/>
       <c r="H30" s="52"/>
       <c r="I30" s="28" t="str">
         <f>F30+G30</f>
@@ -2235,8 +2223,8 @@
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="73"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="71"/>
       <c r="H31" s="52"/>
       <c r="I31" s="28" t="str">
         <f>F31+G31</f>
@@ -2253,8 +2241,8 @@
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="73"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="71"/>
       <c r="H32" s="52"/>
       <c r="I32" s="28" t="str">
         <f>F32+G32</f>
@@ -2271,8 +2259,8 @@
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="73"/>
+      <c r="F33" s="70"/>
+      <c r="G33" s="71"/>
       <c r="H33" s="52"/>
       <c r="I33" s="28" t="str">
         <f>F33+G33</f>
@@ -2289,8 +2277,8 @@
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="73"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="71"/>
       <c r="H34" s="52"/>
       <c r="I34" s="28" t="str">
         <f>F34+G34</f>
@@ -2307,8 +2295,8 @@
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="73"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="71"/>
       <c r="H35" s="52"/>
       <c r="I35" s="28" t="str">
         <f>F35+G35</f>
@@ -2325,8 +2313,8 @@
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="73"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="71"/>
       <c r="H36" s="52"/>
       <c r="I36" s="28" t="str">
         <f>F36+G36</f>
@@ -2343,8 +2331,8 @@
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="73"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="71"/>
       <c r="H37" s="52"/>
       <c r="I37" s="28" t="str">
         <f>F37+G37</f>
@@ -2361,8 +2349,8 @@
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="72"/>
-      <c r="G38" s="73"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="71"/>
       <c r="H38" s="52"/>
       <c r="I38" s="28" t="str">
         <f>F38+G38</f>
@@ -2379,8 +2367,8 @@
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
-      <c r="F39" s="72"/>
-      <c r="G39" s="73"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="71"/>
       <c r="H39" s="52"/>
       <c r="I39" s="28" t="str">
         <f>F39+G39</f>
@@ -2397,8 +2385,8 @@
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="73"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="71"/>
       <c r="H40" s="52"/>
       <c r="I40" s="28" t="str">
         <f>F40+G40</f>
@@ -2415,8 +2403,8 @@
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
-      <c r="F41" s="72"/>
-      <c r="G41" s="73"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="71"/>
       <c r="H41" s="52"/>
       <c r="I41" s="28" t="str">
         <f>F41+G41</f>
@@ -2433,8 +2421,8 @@
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
       <c r="E42" s="17"/>
-      <c r="F42" s="72"/>
-      <c r="G42" s="73"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="71"/>
       <c r="H42" s="52"/>
       <c r="I42" s="28" t="str">
         <f>F42+G42</f>
@@ -2451,8 +2439,8 @@
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
-      <c r="F43" s="72"/>
-      <c r="G43" s="73"/>
+      <c r="F43" s="70"/>
+      <c r="G43" s="71"/>
       <c r="H43" s="52"/>
       <c r="I43" s="28" t="str">
         <f>F43+G43</f>
@@ -2469,8 +2457,8 @@
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
       <c r="E44" s="17"/>
-      <c r="F44" s="72"/>
-      <c r="G44" s="73"/>
+      <c r="F44" s="70"/>
+      <c r="G44" s="71"/>
       <c r="H44" s="52"/>
       <c r="I44" s="28" t="str">
         <f>F44+G44</f>
@@ -2487,8 +2475,8 @@
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
       <c r="E45" s="17"/>
-      <c r="F45" s="72"/>
-      <c r="G45" s="73"/>
+      <c r="F45" s="70"/>
+      <c r="G45" s="71"/>
       <c r="H45" s="52"/>
       <c r="I45" s="28" t="str">
         <f>F45+G45</f>
@@ -2512,7 +2500,7 @@
         <f>SUM(F16:G45)</f>
         <v>0</v>
       </c>
-      <c r="G46" s="75"/>
+      <c r="G46" s="73"/>
       <c r="I46" s="28" t="str">
         <f>SUM(F16:F45)</f>
         <v>0</v>
@@ -2537,14 +2525,14 @@
           </r>
         </is>
       </c>
-      <c r="F47" s="74" t="inlineStr">
+      <c r="F47" s="72" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
           </r>
         </is>
       </c>
-      <c r="G47" s="75"/>
+      <c r="G47" s="73"/>
       <c r="I47" s="28" t="str">
         <f>SUM(G16:G45)</f>
         <v>0</v>
@@ -2563,14 +2551,14 @@
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="23"/>
-      <c r="F48" s="74" t="inlineStr">
+      <c r="F48" s="72" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
           </r>
         </is>
       </c>
-      <c r="G48" s="75"/>
+      <c r="G48" s="73"/>
       <c r="J48" s="52"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2579,7 +2567,7 @@
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="23"/>
-      <c r="F49" s="76"/>
+      <c r="F49" s="74"/>
       <c r="G49" s="60"/>
       <c r="J49" s="52"/>
     </row>
@@ -2589,7 +2577,7 @@
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="23"/>
-      <c r="F50" s="76"/>
+      <c r="F50" s="74"/>
       <c r="G50" s="60"/>
       <c r="J50" s="52"/>
     </row>
@@ -2599,7 +2587,7 @@
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="24"/>
-      <c r="F51" s="76"/>
+      <c r="F51" s="74"/>
       <c r="G51" s="60"/>
       <c r="J51" s="52"/>
     </row>
@@ -2619,7 +2607,7 @@
         <f>SUM(F46:G51)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="75"/>
+      <c r="G52" s="73"/>
       <c r="J52" s="52"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2640,8 +2628,8 @@
           </r>
         </is>
       </c>
-      <c r="F53" s="77"/>
-      <c r="G53" s="75"/>
+      <c r="F53" s="75"/>
+      <c r="G53" s="73"/>
       <c r="J53" s="52"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2650,8 +2638,8 @@
       <c r="C54" s="5"/>
       <c r="D54" s="25"/>
       <c r="E54" s="26"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="75"/>
+      <c r="F54" s="75"/>
+      <c r="G54" s="73"/>
       <c r="J54" s="52"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2660,8 +2648,8 @@
       <c r="C55" s="5"/>
       <c r="D55" s="25"/>
       <c r="E55" s="26"/>
-      <c r="F55" s="77"/>
-      <c r="G55" s="75"/>
+      <c r="F55" s="75"/>
+      <c r="G55" s="73"/>
       <c r="J55" s="52"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2670,8 +2658,8 @@
       <c r="C56" s="5"/>
       <c r="D56" s="25"/>
       <c r="E56" s="26"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="73"/>
       <c r="J56" s="52"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2680,8 +2668,8 @@
       <c r="C57" s="5"/>
       <c r="D57" s="25"/>
       <c r="E57" s="26"/>
-      <c r="F57" s="77"/>
-      <c r="G57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="73"/>
       <c r="J57" s="52"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -2700,7 +2688,7 @@
         <f>SUM(F52-F53-F54-F55-F56-F57)</f>
         <v>0</v>
       </c>
-      <c r="G58" s="78"/>
+      <c r="G58" s="76"/>
       <c r="J58" s="52"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -2780,11 +2768,12 @@
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="F58:G58"/>
     <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F12:G13"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.39370078740157" right="0.39370078740157" top="0.78740157480315" bottom="0.78740157480315" header="0.31496062992126" footer="0.31496062992126"/>

--- a/resources/templates/heyman/roro_contract.xlsx
+++ b/resources/templates/heyman/roro_contract.xlsx
@@ -20,7 +20,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
   <si>
     <r>
-      <t xml:space="preserve">PROFORM CONTRACT</t>
+      <t xml:space="preserve">PROFORMA CONTRACT</t>
     </r>
   </si>
   <si>
@@ -55,7 +55,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -98,7 +98,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -108,7 +108,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -128,7 +128,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -1553,13 +1553,14 @@
       <c r="E1" s="36" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM CONTRACT</t>
+            <t xml:space="preserve">PROFORMA CONTRACT</t>
           </r>
         </is>
       </c>
       <c r="F1" s="53"/>
       <c r="G1" s="54"/>
       <c r="H1" s="12"/>
+      <c r="I1" s="52"/>
       <c r="J1" s="52"/>
     </row>
     <row r="2" spans="1:10">
@@ -1570,11 +1571,21 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
       <c r="G2" s="4"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A3" s="55"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
       <c r="E3" s="9" t="inlineStr">
         <is>
           <r>
@@ -1587,6 +1598,8 @@
         <v>0</v>
       </c>
       <c r="G3" s="56"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
       <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1609,10 +1622,15 @@
         </is>
       </c>
       <c r="G4" s="57"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
       <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A5" s="40"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <r>
@@ -1628,23 +1646,33 @@
         </is>
       </c>
       <c r="G5" s="57"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A6" s="40"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="57"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
       <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A7" s="40"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <r>
@@ -1654,17 +1682,26 @@
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="57"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
       <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A8" s="40"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="9"/>
       <c r="F8" s="44"/>
       <c r="G8" s="57"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
       <c r="J8" s="52"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A9" s="40"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="7"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -1681,6 +1718,8 @@
         </is>
       </c>
       <c r="G9" s="57"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
       <c r="J9" s="52"/>
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1697,6 +1736,8 @@
       <c r="E10" s="58"/>
       <c r="F10" s="58"/>
       <c r="G10" s="59"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
       <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1727,13 +1768,15 @@
         </is>
       </c>
       <c r="G11" s="60"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A12" s="32" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -1749,7 +1792,7 @@
       <c r="E12" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -1761,6 +1804,8 @@
         </is>
       </c>
       <c r="G12" s="62"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
       <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1783,7 +1828,7 @@
       <c r="E13" s="51" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
@@ -1791,13 +1836,20 @@
         <v>23</v>
       </c>
       <c r="G13" s="61"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
       <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="13.5" s="52" customFormat="1">
       <c r="A14" s="8"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="7"/>
       <c r="E14" s="65"/>
+      <c r="F14" s="52"/>
       <c r="G14" s="21"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
       <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1850,6 +1902,8 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
       <c r="J15" s="52"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1887,6 +1941,7 @@
       <c r="G16" s="67">
         <v>1075</v>
       </c>
+      <c r="H16" s="52"/>
       <c r="I16" s="28" t="str">
         <f>F16+G16</f>
         <v>0</v>
@@ -1928,6 +1983,7 @@
       <c r="G17" s="67">
         <v>1075</v>
       </c>
+      <c r="H17" s="52"/>
       <c r="I17" s="28" t="str">
         <f>F17+G17</f>
         <v>0</v>
@@ -1969,6 +2025,7 @@
       <c r="G18" s="67">
         <v>1075</v>
       </c>
+      <c r="H18" s="52"/>
       <c r="I18" s="28" t="str">
         <f>F18+G18</f>
         <v>0</v>
@@ -2010,6 +2067,7 @@
       <c r="G19" s="67">
         <v>1075</v>
       </c>
+      <c r="H19" s="52"/>
       <c r="I19" s="28" t="str">
         <f>F19+G19</f>
         <v>0</v>
@@ -2027,6 +2085,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="68"/>
       <c r="G20" s="69"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="28" t="str">
         <f>F20+G20</f>
         <v>0</v>
@@ -2044,6 +2103,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="68"/>
       <c r="G21" s="69"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="28" t="str">
         <f>F21+G21</f>
         <v>0</v>
@@ -2061,6 +2121,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="68"/>
       <c r="G22" s="69"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="28" t="str">
         <f>F22+G22</f>
         <v>0</v>
@@ -2078,6 +2139,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="68"/>
       <c r="G23" s="69"/>
+      <c r="H23" s="52"/>
       <c r="I23" s="28" t="str">
         <f>F23+G23</f>
         <v>0</v>
@@ -2101,6 +2163,7 @@
       </c>
       <c r="F24" s="68"/>
       <c r="G24" s="69"/>
+      <c r="H24" s="52"/>
       <c r="I24" s="28" t="str">
         <f>F24+G24</f>
         <v>0</v>
@@ -2118,6 +2181,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="68"/>
       <c r="G25" s="69"/>
+      <c r="H25" s="52"/>
       <c r="I25" s="28" t="str">
         <f>F25+G25</f>
         <v>0</v>
@@ -2501,6 +2565,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="73"/>
+      <c r="H46" s="52"/>
       <c r="I46" s="28" t="str">
         <f>SUM(F16:F45)</f>
         <v>0</v>
@@ -2533,6 +2598,7 @@
         </is>
       </c>
       <c r="G47" s="73"/>
+      <c r="H47" s="52"/>
       <c r="I47" s="28" t="str">
         <f>SUM(G16:G45)</f>
         <v>0</v>
@@ -2559,6 +2625,8 @@
         </is>
       </c>
       <c r="G48" s="73"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
       <c r="J48" s="52"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2569,6 +2637,8 @@
       <c r="E49" s="23"/>
       <c r="F49" s="74"/>
       <c r="G49" s="60"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
       <c r="J49" s="52"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2579,6 +2649,8 @@
       <c r="E50" s="23"/>
       <c r="F50" s="74"/>
       <c r="G50" s="60"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
       <c r="J50" s="52"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2589,6 +2661,8 @@
       <c r="E51" s="24"/>
       <c r="F51" s="74"/>
       <c r="G51" s="60"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
       <c r="J51" s="52"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -2608,6 +2682,8 @@
         <v>0</v>
       </c>
       <c r="G52" s="73"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
       <c r="J52" s="52"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2630,6 +2706,8 @@
       </c>
       <c r="F53" s="75"/>
       <c r="G53" s="73"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
       <c r="J53" s="52"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2640,6 +2718,8 @@
       <c r="E54" s="26"/>
       <c r="F54" s="75"/>
       <c r="G54" s="73"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
       <c r="J54" s="52"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2650,6 +2730,8 @@
       <c r="E55" s="26"/>
       <c r="F55" s="75"/>
       <c r="G55" s="73"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
       <c r="J55" s="52"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2660,6 +2742,8 @@
       <c r="E56" s="26"/>
       <c r="F56" s="75"/>
       <c r="G56" s="73"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
       <c r="J56" s="52"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2670,6 +2754,8 @@
       <c r="E57" s="26"/>
       <c r="F57" s="75"/>
       <c r="G57" s="73"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
       <c r="J57" s="52"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -2689,11 +2775,16 @@
         <v>0</v>
       </c>
       <c r="G58" s="76"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
       <c r="J58" s="52"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A59" s="40"/>
       <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
       <c r="F59" s="41" t="inlineStr">
         <is>
           <r>
@@ -2702,26 +2793,56 @@
         </is>
       </c>
       <c r="G59" s="4"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
       <c r="J59" s="52"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A60" s="40"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52"/>
       <c r="G60" s="4"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
       <c r="J60" s="52"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A61" s="40"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="52"/>
+      <c r="F61" s="52"/>
       <c r="G61" s="4"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="52"/>
       <c r="J61" s="52"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A62" s="40"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="52"/>
+      <c r="F62" s="52"/>
       <c r="G62" s="4"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="52"/>
       <c r="J62" s="52"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A63" s="40"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
       <c r="G63" s="4"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="52"/>
       <c r="J63" s="52"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -2732,6 +2853,8 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1"/>
+      <c r="H64" s="52"/>
+      <c r="I64" s="52"/>
       <c r="J64" s="52"/>
     </row>
   </sheetData>

--- a/resources/templates/heyman/roro_contract.xlsx
+++ b/resources/templates/heyman/roro_contract.xlsx
@@ -25,7 +25,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
+      <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-10-9009-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
     </r>
   </si>
   <si>
@@ -1567,7 +1567,7 @@
       <c r="A2" s="37" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-505-355-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
+            <t xml:space="preserve">HEYMAN LTD., #513, THE PARK 365, 50 Seonyudong1-ro, Yeongdeungpo-gu, Seoul, Korea TEL:82-10-9009-9977 FAX:82-505-366-9977 EMAIL : heyman99888@gmail.com</t>
           </r>
         </is>
       </c>
